--- a/football/data/quasi_stake_tracker.xlsx
+++ b/football/data/quasi_stake_tracker.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,6 +565,16 @@
       <c r="AD1" t="inlineStr">
         <is>
           <t>Result Notes</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Opportunity ID</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Category</t>
         </is>
       </c>
     </row>
